--- a/codelists/stroke_raw.xlsx
+++ b/codelists/stroke_raw.xlsx
@@ -11901,7 +11901,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>416991000006112</t>
+          <t>300348012</t>
         </is>
       </c>
       <c r="B185" s="1" t="n">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Fyu55</t>
+          <t>G65y</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Fyu5500</t>
+          <t>G65y.00</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Transient cerebral ischemia</t>
+          <t>Other transient cerebral ischaemia</t>
         </is>
       </c>
       <c r="H185" s="1" t="n">
@@ -11968,7 +11968,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>300348012</t>
+          <t>416991000006112</t>
         </is>
       </c>
       <c r="B186" s="1" t="n">
@@ -11976,12 +11976,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>G65y</t>
+          <t>Fyu55</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>G65y.00</t>
+          <t>Fyu5500</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Other transient cerebral ischaemia</t>
+          <t>Transient cerebral ischemia</t>
         </is>
       </c>
       <c r="H186" s="1" t="n">
@@ -12092,7 +12092,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1227592012</t>
+          <t>460286014</t>
         </is>
       </c>
       <c r="B188" s="1" t="n">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ZV125-2</t>
+          <t>ZV125</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ZV12512</t>
+          <t>ZV12500</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[V]Personal history of cerebrovascular accident (CVA)</t>
+          <t>[V]Personal history of circulatory system disease</t>
         </is>
       </c>
       <c r="H188" s="1" t="n">
@@ -12128,20 +12128,14 @@
       </c>
       <c r="I188" s="1" t="n"/>
       <c r="J188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1" t="n"/>
       <c r="L188" s="1" t="n"/>
       <c r="M188" s="1" t="n"/>
-      <c r="N188" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O188" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P188" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="N188" s="1" t="n"/>
+      <c r="O188" s="1" t="n"/>
+      <c r="P188" s="1" t="n"/>
       <c r="Q188" s="1" t="n"/>
       <c r="R188" s="1" t="n"/>
       <c r="S188" s="1" t="n"/>
@@ -12151,7 +12145,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>460286014</t>
+          <t>1227592012</t>
         </is>
       </c>
       <c r="B189" s="1" t="n">
@@ -12159,12 +12153,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ZV125</t>
+          <t>ZV125-2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ZV12500</t>
+          <t>ZV12512</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12179,7 +12173,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[V]Personal history of circulatory system disease</t>
+          <t>[V]Personal history of cerebrovascular accident (CVA)</t>
         </is>
       </c>
       <c r="H189" s="1" t="n">
@@ -12187,14 +12181,20 @@
       </c>
       <c r="I189" s="1" t="n"/>
       <c r="J189" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1" t="n"/>
       <c r="L189" s="1" t="n"/>
       <c r="M189" s="1" t="n"/>
-      <c r="N189" s="1" t="n"/>
-      <c r="O189" s="1" t="n"/>
-      <c r="P189" s="1" t="n"/>
+      <c r="N189" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O189" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P189" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="Q189" s="1" t="n"/>
       <c r="R189" s="1" t="n"/>
       <c r="S189" s="1" t="n"/>
@@ -21941,7 +21941,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>402209015</t>
+          <t>316140013</t>
         </is>
       </c>
       <c r="B355" s="1" t="n">
@@ -21949,12 +21949,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Q200z</t>
+          <t>Q2001</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Q200z00</t>
+          <t>Q200100</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Subdural or cerebral haemorrhage due to birth trauma NOS</t>
+          <t>Subdural haemorrhage unspecified, due to birth trauma</t>
         </is>
       </c>
       <c r="H355" s="1" t="n">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="I355" s="1" t="n"/>
       <c r="J355" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K355" s="1" t="n"/>
       <c r="L355" s="1" t="n"/>
@@ -21994,7 +21994,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>316140013</t>
+          <t>402209015</t>
         </is>
       </c>
       <c r="B356" s="1" t="n">
@@ -22002,12 +22002,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Q2001</t>
+          <t>Q200z</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Q200100</t>
+          <t>Q200z00</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Subdural haemorrhage unspecified, due to birth trauma</t>
+          <t>Subdural or cerebral haemorrhage due to birth trauma NOS</t>
         </is>
       </c>
       <c r="H356" s="1" t="n">
@@ -22030,7 +22030,7 @@
       </c>
       <c r="I356" s="1" t="n"/>
       <c r="J356" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K356" s="1" t="n"/>
       <c r="L356" s="1" t="n"/>
@@ -34595,7 +34595,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>7378401000006111</t>
+          <t>39791000006115</t>
         </is>
       </c>
       <c r="B587" s="1" t="n">
@@ -34603,10 +34603,14 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>^ESCTTR737840</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr"/>
+          <t>S6313</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>S631300</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
           <t>450418003</t>
@@ -34619,7 +34623,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Traumatic intracerebral hemorrhage</t>
+          <t>Oth cerebral h'ge inj + open intracran wnd+1-24hr loss consc</t>
         </is>
       </c>
       <c r="H587" s="1" t="n">
@@ -34627,7 +34631,7 @@
       </c>
       <c r="I587" s="1" t="n"/>
       <c r="J587" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K587" s="1" t="n"/>
       <c r="L587" s="1" t="n"/>
@@ -34648,7 +34652,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>39791000006115</t>
+          <t>30981000006112</t>
         </is>
       </c>
       <c r="B588" s="1" t="n">
@@ -34656,12 +34660,12 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>S6313</t>
+          <t>S6300</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>S631300</t>
+          <t>S630000</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -34676,7 +34680,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Oth cerebral h'ge inj + open intracran wnd+1-24hr loss consc</t>
+          <t>Oth cerebral h'ge inj no open intracran wnd+unspec consc</t>
         </is>
       </c>
       <c r="H588" s="1" t="n">
@@ -34705,7 +34709,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>30981000006112</t>
+          <t>7378401000006111</t>
         </is>
       </c>
       <c r="B589" s="1" t="n">
@@ -34713,14 +34717,10 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>S6300</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>S630000</t>
-        </is>
-      </c>
+          <t>^ESCTTR737840</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
           <t>450418003</t>
@@ -34733,7 +34733,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Oth cerebral h'ge inj no open intracran wnd+unspec consc</t>
+          <t>Traumatic intracerebral hemorrhage</t>
         </is>
       </c>
       <c r="H589" s="1" t="n">
@@ -34741,7 +34741,7 @@
       </c>
       <c r="I589" s="1" t="n"/>
       <c r="J589" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K589" s="1" t="n"/>
       <c r="L589" s="1" t="n"/>
@@ -37503,7 +37503,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>123311000006115</t>
+          <t>123431000006119</t>
         </is>
       </c>
       <c r="B643" s="1" t="n">
@@ -37511,12 +37511,12 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>S620z</t>
+          <t>S6200</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>S620z00</t>
+          <t>S620000</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Subarach h'ge inj no open intracran wnd + concussion unspec</t>
+          <t>Subarachnoid h'ge inj no open intracran wound + unspec consc</t>
         </is>
       </c>
       <c r="H643" s="1" t="n">
@@ -37560,7 +37560,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>123431000006119</t>
+          <t>123311000006115</t>
         </is>
       </c>
       <c r="B644" s="1" t="n">
@@ -37568,12 +37568,12 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>S6200</t>
+          <t>S620z</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>S620000</t>
+          <t>S620z00</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -37588,7 +37588,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Subarachnoid h'ge inj no open intracran wound + unspec consc</t>
+          <t>Subarach h'ge inj no open intracran wnd + concussion unspec</t>
         </is>
       </c>
       <c r="H644" s="1" t="n">
@@ -37984,7 +37984,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>39731000006119</t>
+          <t>39711000006113</t>
         </is>
       </c>
       <c r="B652" s="1" t="n">
@@ -37992,12 +37992,12 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>S6304</t>
+          <t>S631z</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>S630400</t>
+          <t>S631z00</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
@@ -38012,7 +38012,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Oth cereb h'ge inj no open intracran wnd+&gt;24hr LOC +recovery</t>
+          <t>Oth cereb h'ge inj + open intracran wnd+concussion unspec</t>
         </is>
       </c>
       <c r="H652" s="1" t="n">
@@ -38041,7 +38041,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>39711000006113</t>
+          <t>39731000006119</t>
         </is>
       </c>
       <c r="B653" s="1" t="n">
@@ -38049,12 +38049,12 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>S631z</t>
+          <t>S6304</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>S631z00</t>
+          <t>S630400</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -38069,7 +38069,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Oth cereb h'ge inj + open intracran wnd+concussion unspec</t>
+          <t>Oth cereb h'ge inj no open intracran wnd+&gt;24hr LOC +recovery</t>
         </is>
       </c>
       <c r="H653" s="1" t="n">
